--- a/measurements/20260904_154429_checkerboard_pilot/20260904_154429_checkerboard_pilot/checkerboard_pse_result_psignifit.xlsx
+++ b/measurements/20260904_154429_checkerboard_pilot/20260904_154429_checkerboard_pilot/checkerboard_pse_result_psignifit.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="51" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="68" uniqueCount="17">
   <si>
     <t>participant_id</t>
   </si>
